--- a/ZT411_300dpi_헤드_업체비교.xlsx
+++ b/ZT411_300dpi_헤드_업체비교.xlsx
@@ -113,12 +113,636 @@
         </r>
       </text>
     </comment>
+    <comment ref="D21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">추정값</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">($80): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">헤드 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">10</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">개</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">약 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3~5kg) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">중국→한국 특송 기준 대략치</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. EXW </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">조건이라 중국 내 픽업</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">수출통관 비용이 추가될 수 있음</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">업체 운임 견적 받으면 수정</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">프린터 부품</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(HS 8443.99)</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">은 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ITA </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">품목으로 기본관세 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0%</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">로 추정</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">관세사 확인 필요</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">부가세 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">= (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">과세가격 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">+ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">관세</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">) × 10%. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">사업자 매입세액 공제</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">환급</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">가능</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">추정값</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">특송 통관수수료</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">관세사 수수료 등 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">실제 청구액으로 수정</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">추정값</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: T/T </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">해외송금 수수료</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">전신료 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">은행별 상이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">추정값</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">($80). FOB </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">조건 — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Colortek</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">이 주소 받으면 운송비 견적 준다고 함</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">견적 받으면 수정</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">견적서 상 주문 수량이 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1.0</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">으로 표기됨 → </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">10</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">개 기준 단가 재확인 필요</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">추정값</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">($80). EXW </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">조건 — 중국 내 픽업</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">수출통관 비용 추가 가능</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">견적 받으면 수정</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
   <si>
     <r>
       <rPr>
@@ -415,7 +1039,18 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">프린트헤드</t>
+      <t xml:space="preserve">프린트헤드 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="18"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(P1058930-010)</t>
     </r>
   </si>
   <si>
@@ -726,9 +1361,277 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+    <t xml:space="preserve">주문 수량</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모델번호</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Part No.)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P1058930-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미기재</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정품 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상태</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Original new (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제조사 정품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)
+Brand new, unused
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제조사 정품 포장 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출고 전 테스트</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">original print head
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상세정보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: "for ZT410, 300dpi" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Original Zebra ZT411 300dpi printhead
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상세 정보 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선적조건 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출발지</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">EXW / Guangzhou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOB / Shenzhen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXW / Suzhou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">결제방식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T/T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">납기일정</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제 후 </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
@@ -739,13 +1642,677 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 합계</t>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 이내
+예상 발송일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-11-13</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예상 발송일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-11-13</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예상 발송일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-11-14</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">샘플</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제공 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">O / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무료 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">운임 구매자 부담</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인 후 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제공 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">O</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">비고</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">• 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">곳 중 최저가
+• 판매자 소개는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Guangzhou ASON, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프린터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">헤드 제조 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 알리바바 등록 회사명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Jiamei)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 다름 → 계약 주체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수취 계좌 확인 필요
+• 주력이 중고 장비 → 새제품 재확인</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">• 알리바바 경력 최장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">왕관 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개
+• 주소 알려주면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 운송비 별도 견적 예정
+• 상세정보의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"ZT410" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표기 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ZT411 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">호환 확인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(ZT410/411 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">동일 헤드로 알려짐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">• 왕관 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개
+• 모델번호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제조건 미기재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수량 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 기준 견적
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">더 좋은 가격 제시 가능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">" → 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 단가 네고 여지</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="18"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">총 비용 계산 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="18"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="18"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수입 원가</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="18"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="18"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주문 수량 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="18"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제품가 합계</t>
     </r>
     <r>
       <rPr>
@@ -765,21 +2332,56 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 합계</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국제운송비</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(USD)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과세가격 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CIF(USD)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과세가격</t>
     </r>
     <r>
       <rPr>
@@ -815,31 +2417,43 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">정품 표기</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Genuine Zebra ZT411 300DPI Printhead
-(Zebra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정품 포장 사진 있음</t>
-    </r>
-    <r>
-      <rPr>
+    <t xml:space="preserve">관세율</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">관세</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원화</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
@@ -852,26 +2466,38 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">original Zebra ZT411 300dpi
-(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제품 사진 없음</t>
-    </r>
-    <r>
-      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수입 부가세 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원화</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
@@ -884,26 +2510,59 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Original Zebra ZT411 300dpi
-(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">제품 사진 없음</t>
-    </r>
-    <r>
-      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통관</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기타 수수료</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원화</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
@@ -914,45 +2573,19 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">재고여부</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미확인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">납기일정</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">샘플 리드타임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 </t>
-    </r>
-    <r>
-      <rPr>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">해외송금 수수료</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
@@ -963,100 +2596,274 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">샘플비 구매자 부담</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">본 발주 납기 미확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">비고</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• 단가 최저 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">곳 중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)
-• </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">업력 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원화</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">총 비용</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원화</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개당 원가</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원화</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부가세 환급 시 실부담</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원화</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국내 매입 대비 절감액</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원화</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 비교 제외 업체 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">총 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건 견적 중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">• Hangzhou Codewel New Material ($232, 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1064,374 +2871,707 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현장 자재 검수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">왕관 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최저가지만 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Hot Selling Thermal Printhead ZT410/ZT41…" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표기로 정품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Genuine/Original) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표기 없음 → 호환품 가능성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정품 확인 시 후보 편입</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">• Jiangsu Wishbigger Information ($280, 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">협력사 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">곳
-• 등급 왕관 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개
-• 주력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중고 프린터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">왕관 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최고가 수준 대비 등급 낮음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">• Shenzhen Protex ($1,275) / Chongqing Greensun ($1,090) — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">헤드가 아닌 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ZT411 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프린터 본체 견적</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 공통 사항 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">알리바바 구매 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">부품 → 새제품 여부 확인 필요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• 알리바바 경력 최장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">년</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)
-• </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등급 왕관 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경험 다수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배지
-• 주력에 프린트헤드 포함</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• 등급 왕관 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개
-• 주력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">바코드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">거래는 알리바바 플랫폼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Trade Assurance)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 통해 진행 — 결제수단별 수수료 발생 가능</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표기 단가는 제품가 기준이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국제운송비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수입 부가세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10%)·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통관수수료는 별도</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">관세 부담 주체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(DAP/DDP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등 인코텀즈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 업체별 확인 후 최종 비교 필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원화 환산은 상단 환율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(D2) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제 시점 환율에 따라 변동</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정품 파트번호 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P1058930-010(Jiamei·Colortek </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">견적서 기재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">새제품 여부</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불량 보증기간 발주 전 확인 필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">총 비용의 노란 셀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">운송비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">관세율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수수료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 추정값 → 업체 운임 견적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">카드 프린터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">스캐너</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 비교 제외 업체 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실제 청구액으로 수정하면 자동 재계산</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">총 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+      <t xml:space="preserve">7. EXW(Jiamei·Scantech)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 공장 인도 조건 → 중국 내 운송</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건 견적 중</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수출통관 비용이 추가될 수 있어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">FOB(Colortek)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보다 실비용이 더 들 수 있음</t>
     </r>
   </si>
   <si>
@@ -1442,15 +3582,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">• Hangzhou Codewel New Material ($232, 8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">년</t>
+      <t xml:space="preserve">8. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">견적 요청 만료 </t>
     </r>
     <r>
       <rPr>
@@ -1459,624 +3599,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">왕관 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최저가지만 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"Hot Selling Thermal Printhead ZT410/ZT41…" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">표기로 정품</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Genuine/Original) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">표기 없음 → 호환품 가능성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정품 확인 시 후보 편입</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">• Jiangsu Wishbigger Information ($280, 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">년</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">왕관 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최고가 수준 대비 등급 낮음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">• Shenzhen Protex ($1,275) / Chongqing Greensun ($1,090) — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">헤드가 아닌 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ZT411 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">프린터 본체 견적</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 공통 사항 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">알리바바 구매 기준</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">거래는 알리바바 플랫폼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Trade Assurance)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">을 통해 진행 — 결제수단별 수수료 발생 가능</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">표기 단가는 제품가 기준이며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">국제운송비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수입 부가세</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10%)·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">통관수수료는 별도</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관세 부담 주체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(DAP/DDP </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">등 인코텀즈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 업체별 확인 후 최종 비교 필요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원화 환산은 상단 환율</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(D2) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기준이며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제 시점 환율에 따라 변동</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정품 파트번호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(ZT411 300dpi: P1058930-010 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">추정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">발주 전 확인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">새제품 여부</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">불량 보증기간 발주 전 확인 필요</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">견적 요청 수량 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 기준 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요청 만료 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-29) — 10</t>
+      <t xml:space="preserve">2026-10-29 — 10</t>
     </r>
     <r>
       <rPr>
@@ -2092,13 +3615,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0\원"/>
+    <numFmt numFmtId="168" formatCode="#,##0\개"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2223,6 +3748,13 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
@@ -2250,7 +3782,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2291,6 +3823,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
   </fills>
@@ -2343,7 +3881,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2400,15 +3938,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2420,19 +3950,39 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2491,7 +4041,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -2697,7 +4247,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F27"/>
+  <dimension ref="B2:F47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -2785,174 +4335,495 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="15" t="n">
-        <f aca="false">D7*10</f>
-        <v>2400</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <f aca="false">E7*10</f>
-        <v>2800</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <f aca="false">F7*10</f>
-        <v>2700</v>
+      <c r="D9" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <f aca="false">D9*$D$2</f>
-        <v>3267600</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <f aca="false">E9*$D$2</f>
-        <v>3812200</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <f aca="false">F9*$D$2</f>
-        <v>3676050</v>
+      <c r="D10" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="18" t="s">
+      <c r="D11" s="16" t="s">
         <v>17</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>19</v>
+      <c r="D13" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="21" t="s">
-        <v>26</v>
+    <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="22" t="s">
-        <v>27</v>
+    <row r="16" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="22" t="s">
-        <v>28</v>
-      </c>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="22" t="s">
-        <v>29</v>
+    <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="20" t="n">
+        <f aca="false">D7*D9</f>
+        <v>2400</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <f aca="false">E7*E9</f>
+        <v>2800</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <f aca="false">F7*F9</f>
+        <v>2700</v>
+      </c>
+    </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="21" t="s">
-        <v>30</v>
+      <c r="B21" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="22" t="s">
-        <v>31</v>
+      <c r="B22" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="20" t="n">
+        <f aca="false">D20+D21</f>
+        <v>2480</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <f aca="false">E20+E21</f>
+        <v>2880</v>
+      </c>
+      <c r="F22" s="20" t="n">
+        <f aca="false">F20+F21</f>
+        <v>2780</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="22" t="s">
-        <v>32</v>
+      <c r="B23" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <f aca="false">D22*$D$2</f>
+        <v>3376520</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <f aca="false">E22*$D$2</f>
+        <v>3921120</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <f aca="false">F22*$D$2</f>
+        <v>3784970</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="22" t="s">
-        <v>33</v>
+      <c r="B24" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="22" t="s">
-        <v>34</v>
+      <c r="B25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <f aca="false">ROUND(D23*D24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <f aca="false">ROUND(E23*E24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <f aca="false">ROUND(F23*F24,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="22" t="s">
-        <v>35</v>
+      <c r="B26" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <f aca="false">ROUND((D23+D25)*0.1,0)</f>
+        <v>337652</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <f aca="false">ROUND((E23+E25)*0.1,0)</f>
+        <v>392112</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <f aca="false">ROUND((F23+F25)*0.1,0)</f>
+        <v>378497</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="22" t="s">
-        <v>36</v>
+      <c r="B27" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="19" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*10,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D29" s="23" t="n">
+        <f aca="false">D23+D25+D26+D27+D28</f>
+        <v>3764172</v>
+      </c>
+      <c r="E29" s="23" t="n">
+        <f aca="false">E23+E25+E26+E27+E28</f>
+        <v>4363232</v>
+      </c>
+      <c r="F29" s="23" t="n">
+        <f aca="false">F23+F25+F26+F27+F28</f>
+        <v>4213467</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="19" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <f aca="false">ROUND(D29/D9,0)</f>
+        <v>376417</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <f aca="false">ROUND(E29/E9,0)</f>
+        <v>436323</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <f aca="false">ROUND(F29/F9,0)</f>
+        <v>421347</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="19" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*10,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <f aca="false">D29-D26</f>
+        <v>3426520</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <f aca="false">E29-E26</f>
+        <v>3971120</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <f aca="false">F29-F26</f>
+        <v>3834970</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="13" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*D9-D31,"국내단가 입력 필요")</f>
+        <v>국내단가 입력 필요</v>
+      </c>
+      <c r="E32" s="13" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*E9-E31,"국내단가 입력 필요")</f>
+        <v>국내단가 입력 필요</v>
+      </c>
+      <c r="F32" s="13" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*F9-F31,"국내단가 입력 필요")</f>
+        <v>국내단가 입력 필요</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="25" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D7:F7">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>D7=MIN($D$7:$F$7)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D8:F8">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>D8=MIN($D$8:$F$8)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D10:F10">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>D10=MIN($D$10:$F$10)</formula>
+  <conditionalFormatting sqref="D29:F29">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>D29=MIN($D$29:$F$29)</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/ZT411_300dpi_헤드_업체비교.xlsx
+++ b/ZT411_300dpi_헤드_업체비교.xlsx
@@ -113,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D21" authorId="0">
+    <comment ref="D23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -121,7 +121,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">추정값</t>
+          <t xml:space="preserve">업체 운임 견적 받으면 입력 </t>
         </r>
         <r>
           <rPr>
@@ -129,7 +129,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">($80): </t>
+          <t xml:space="preserve">(EXW: </t>
         </r>
         <r>
           <rPr>
@@ -137,7 +137,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">헤드 </t>
+          <t xml:space="preserve">중국 내 픽업</t>
         </r>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">·</t>
         </r>
         <r>
           <rPr>
@@ -153,7 +153,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">개</t>
+          <t xml:space="preserve">수출통관 비용 포함 여부 확인</t>
         </r>
         <r>
           <rPr>
@@ -161,171 +161,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">(</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">약 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">3~5kg) </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">중국→한국 특송 기준 대략치</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">. EXW </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">조건이라 중국 내 픽업</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">·</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">수출통관 비용이 추가될 수 있음</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">. </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">업체 운임 견적 받으면 수정</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D24" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">프린터 부품</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">(HS 8443.99)</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">은 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">ITA </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">품목으로 기본관세 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">0%</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">로 추정</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">. </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">관세사 확인 필요</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">.</t>
+          <t xml:space="preserve">)</t>
         </r>
       </text>
     </comment>
@@ -337,7 +173,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">부가세 </t>
+          <t xml:space="preserve">관세사 확인 후 입력 </t>
         </r>
         <r>
           <rPr>
@@ -345,7 +181,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">= (</t>
+          <t xml:space="preserve">(</t>
         </r>
         <r>
           <rPr>
@@ -353,7 +189,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">과세가격 </t>
+          <t xml:space="preserve">예</t>
         </r>
         <r>
           <rPr>
@@ -361,7 +197,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">+ </t>
+          <t xml:space="preserve">: 0%</t>
         </r>
         <r>
           <rPr>
@@ -369,7 +205,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">관세</t>
+          <t xml:space="preserve">면 </t>
         </r>
         <r>
           <rPr>
@@ -377,7 +213,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">) × 10%. </t>
+          <t xml:space="preserve">0 </t>
         </r>
         <r>
           <rPr>
@@ -385,99 +221,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">사업자 매입세액 공제</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">(</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">환급</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">) </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">가능</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D27" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">추정값</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">특송 통관수수료</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">·</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">관세사 수수료 등 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">(</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">실제 청구액으로 수정</t>
+          <t xml:space="preserve">입력</t>
         </r>
         <r>
           <rPr>
@@ -497,7 +241,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">추정값</t>
+          <t xml:space="preserve">부가세 </t>
         </r>
         <r>
           <rPr>
@@ -505,7 +249,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">: T/T </t>
+          <t xml:space="preserve">= (</t>
         </r>
         <r>
           <rPr>
@@ -513,7 +257,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">해외송금 수수료</t>
+          <t xml:space="preserve">과세가격 </t>
         </r>
         <r>
           <rPr>
@@ -521,7 +265,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">+</t>
+          <t xml:space="preserve">+ </t>
         </r>
         <r>
           <rPr>
@@ -529,7 +273,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">전신료 </t>
+          <t xml:space="preserve">관세</t>
         </r>
         <r>
           <rPr>
@@ -537,6 +281,22 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">) × 10%. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">사업자 매입세액 공제</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">(</t>
         </r>
         <r>
@@ -545,7 +305,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">은행별 상이</t>
+          <t xml:space="preserve">환급</t>
         </r>
         <r>
           <rPr>
@@ -553,11 +313,19 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">)</t>
+          <t xml:space="preserve">) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">가능</t>
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0">
+    <comment ref="D29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -565,7 +333,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">추정값</t>
+          <t xml:space="preserve">실제 청구액 입력 </t>
         </r>
         <r>
           <rPr>
@@ -573,7 +341,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">($80). FOB </t>
+          <t xml:space="preserve">(</t>
         </r>
         <r>
           <rPr>
@@ -581,6 +349,62 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">특송 통관수수료</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">·</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">관세사 수수료 등</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">실제 송금 수수료 입력</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">FOB </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">조건 — </t>
         </r>
         <r>
@@ -613,7 +437,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">견적 받으면 수정</t>
+          <t xml:space="preserve">받으면 입력</t>
         </r>
         <r>
           <rPr>
@@ -669,7 +493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0">
+    <comment ref="F23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -677,7 +501,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">추정값</t>
+          <t xml:space="preserve">업체 운임 견적 받으면 입력 </t>
         </r>
         <r>
           <rPr>
@@ -685,7 +509,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">($80). EXW </t>
+          <t xml:space="preserve">(EXW </t>
         </r>
         <r>
           <rPr>
@@ -693,7 +517,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">조건 — 중국 내 픽업</t>
+          <t xml:space="preserve">조건</t>
         </r>
         <r>
           <rPr>
@@ -701,39 +525,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">·</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">수출통관 비용 추가 가능</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">. </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">견적 받으면 수정</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">.</t>
+          <t xml:space="preserve">)</t>
         </r>
       </text>
     </comment>
@@ -742,7 +534,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
   <si>
     <r>
       <rPr>
@@ -1816,6 +1608,120 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">재고여부</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미확인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결제 후 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일 이내 출고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">미확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">담당자</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미기재 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Guangzhou ASON </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명의로 소개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Chen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simon Li (Simo)</t>
+  </si>
+  <si>
     <t xml:space="preserve">비고</t>
   </si>
   <si>
@@ -3433,7 +3339,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">총 비용의 노란 셀</t>
+      <t xml:space="preserve">총 비용의 노란 빈칸</t>
     </r>
     <r>
       <rPr>
@@ -3501,7 +3407,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">은 추정값 → 업체 운임 견적</t>
+      <t xml:space="preserve">은 미확정 → 확인되는 대로 입력하면 총 비용 자동 재계산 </t>
     </r>
     <r>
       <rPr>
@@ -3510,15 +3416,41 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">실제 청구액으로 수정하면 자동 재계산</t>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빈칸은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 계산됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -4247,7 +4179,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F47"/>
+  <dimension ref="B2:F49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -4453,361 +4385,369 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="15"/>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="17" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>35</v>
       </c>
       <c r="F16" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="C17" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+    <row r="18" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <f aca="false">D7*D9</f>
-        <v>2400</v>
-      </c>
-      <c r="E20" s="20" t="n">
-        <f aca="false">E7*E9</f>
-        <v>2800</v>
-      </c>
-      <c r="F20" s="20" t="n">
-        <f aca="false">F7*F9</f>
-        <v>2700</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="20" t="n">
-        <f aca="false">D20+D21</f>
-        <v>2480</v>
+        <f aca="false">D7*D9</f>
+        <v>2400</v>
       </c>
       <c r="E22" s="20" t="n">
-        <f aca="false">E20+E21</f>
-        <v>2880</v>
+        <f aca="false">E7*E9</f>
+        <v>2800</v>
       </c>
       <c r="F22" s="20" t="n">
-        <f aca="false">F20+F21</f>
-        <v>2780</v>
+        <f aca="false">F7*F9</f>
+        <v>2700</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="13" t="n">
-        <f aca="false">D22*$D$2</f>
-        <v>3376520</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <f aca="false">E22*$D$2</f>
-        <v>3921120</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <f aca="false">F22*$D$2</f>
-        <v>3784970</v>
-      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="21" t="n">
-        <v>0</v>
+      <c r="D24" s="20" t="n">
+        <f aca="false">D22+D23</f>
+        <v>2400</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <f aca="false">E22+E23</f>
+        <v>2800</v>
+      </c>
+      <c r="F24" s="20" t="n">
+        <f aca="false">F22+F23</f>
+        <v>2700</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="13" t="n">
-        <f aca="false">ROUND(D23*D24,0)</f>
-        <v>0</v>
+        <f aca="false">D24*$D$2</f>
+        <v>3267600</v>
       </c>
       <c r="E25" s="13" t="n">
-        <f aca="false">ROUND(E23*E24,0)</f>
-        <v>0</v>
+        <f aca="false">E24*$D$2</f>
+        <v>3812200</v>
       </c>
       <c r="F25" s="13" t="n">
-        <f aca="false">ROUND(F23*F24,0)</f>
-        <v>0</v>
+        <f aca="false">F24*$D$2</f>
+        <v>3676050</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="13" t="n">
-        <f aca="false">ROUND((D23+D25)*0.1,0)</f>
-        <v>337652</v>
-      </c>
-      <c r="E26" s="13" t="n">
-        <f aca="false">ROUND((E23+E25)*0.1,0)</f>
-        <v>392112</v>
-      </c>
-      <c r="F26" s="13" t="n">
-        <f aca="false">ROUND((F23+F25)*0.1,0)</f>
-        <v>378497</v>
-      </c>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="12" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>30000</v>
+      <c r="D27" s="13" t="n">
+        <f aca="false">ROUND(D25*D26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <f aca="false">ROUND(E25*E26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <f aca="false">ROUND(F25*F26,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C28" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>20000</v>
+      <c r="D28" s="13" t="n">
+        <f aca="false">ROUND((D25+D27)*0.1,0)</f>
+        <v>326760</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <f aca="false">ROUND((E25+E27)*0.1,0)</f>
+        <v>381220</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <f aca="false">ROUND((F25+F27)*0.1,0)</f>
+        <v>367605</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="19" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8*10,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D29" s="23" t="n">
-        <f aca="false">D23+D25+D26+D27+D28</f>
-        <v>3764172</v>
-      </c>
-      <c r="E29" s="23" t="n">
-        <f aca="false">E23+E25+E26+E27+E28</f>
-        <v>4363232</v>
-      </c>
-      <c r="F29" s="23" t="n">
-        <f aca="false">F23+F25+F26+F27+F28</f>
-        <v>4213467</v>
-      </c>
+      <c r="B29" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="19" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D30" s="13" t="n">
-        <f aca="false">ROUND(D29/D9,0)</f>
-        <v>376417</v>
-      </c>
-      <c r="E30" s="13" t="n">
-        <f aca="false">ROUND(E29/E9,0)</f>
-        <v>436323</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <f aca="false">ROUND(F29/F9,0)</f>
-        <v>421347</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="9" t="s">
-        <v>49</v>
+      <c r="B31" s="22" t="s">
+        <v>54</v>
       </c>
       <c r="C31" s="19" t="str">
         <f aca="false">IF(ISNUMBER($C$8),$C$8*10,"-")</f>
         <v>-</v>
       </c>
-      <c r="D31" s="13" t="n">
-        <f aca="false">D29-D26</f>
-        <v>3426520</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <f aca="false">E29-E26</f>
-        <v>3971120</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <f aca="false">F29-F26</f>
-        <v>3834970</v>
+      <c r="D31" s="23" t="n">
+        <f aca="false">D25+D27+D28+D29+D30</f>
+        <v>3594360</v>
+      </c>
+      <c r="E31" s="23" t="n">
+        <f aca="false">E25+E27+E28+E29+E30</f>
+        <v>4193420</v>
+      </c>
+      <c r="F31" s="23" t="n">
+        <f aca="false">F25+F27+F28+F29+F30</f>
+        <v>4043655</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="19" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <f aca="false">ROUND(D31/D9,0)</f>
+        <v>359436</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <f aca="false">ROUND(E31/E9,0)</f>
+        <v>419342</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <f aca="false">ROUND(F31/F9,0)</f>
+        <v>404366</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="19" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*10,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <f aca="false">D31-D28</f>
+        <v>3267600</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <f aca="false">E31-E28</f>
+        <v>3812200</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <f aca="false">F31-F28</f>
+        <v>3676050</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="13" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8*D9-D31,"국내단가 입력 필요")</f>
+      <c r="D34" s="13" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*D9-D33,"국내단가 입력 필요")</f>
         <v>국내단가 입력 필요</v>
       </c>
-      <c r="E32" s="13" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8*E9-E31,"국내단가 입력 필요")</f>
+      <c r="E34" s="13" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*E9-E33,"국내단가 입력 필요")</f>
         <v>국내단가 입력 필요</v>
       </c>
-      <c r="F32" s="13" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8*F9-F31,"국내단가 입력 필요")</f>
+      <c r="F34" s="13" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*F9-F33,"국내단가 입력 필요")</f>
         <v>국내단가 입력 필요</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="25" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="25" t="s">
-        <v>53</v>
+      <c r="B36" s="24" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="25" t="s">
-        <v>54</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="25" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="24" t="s">
-        <v>55</v>
+      <c r="B39" s="25" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="25" t="s">
-        <v>57</v>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="24" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="25" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="25" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="25" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="25" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="25" t="s">
-        <v>63</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="25" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -4821,9 +4761,9 @@
       <formula>D8=MIN($D$8:$F$8)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D29:F29">
+  <conditionalFormatting sqref="D31:F31">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>D29=MIN($D$29:$F$29)</formula>
+      <formula>D31=MIN($D$31:$F$31)</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/ZT411_300dpi_헤드_업체비교.xlsx
+++ b/ZT411_300dpi_헤드_업체비교.xlsx
@@ -113,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D23" authorId="0">
+    <comment ref="D22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -165,7 +165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0">
+    <comment ref="D25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -230,6 +230,98 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">부가세 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">= (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">과세가격 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">+ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">관세</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">) × 10%. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">사업자 매입세액 공제</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">환급</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">가능</t>
         </r>
       </text>
     </comment>
@@ -241,7 +333,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">부가세 </t>
+          <t xml:space="preserve">실제 청구액 입력 </t>
         </r>
         <r>
           <rPr>
@@ -249,7 +341,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">= (</t>
+          <t xml:space="preserve">(</t>
         </r>
         <r>
           <rPr>
@@ -257,7 +349,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">과세가격 </t>
+          <t xml:space="preserve">특송 통관수수료</t>
         </r>
         <r>
           <rPr>
@@ -265,7 +357,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">+ </t>
+          <t xml:space="preserve">·</t>
         </r>
         <r>
           <rPr>
@@ -273,7 +365,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">관세</t>
+          <t xml:space="preserve">관세사 수수료 등</t>
         </r>
         <r>
           <rPr>
@@ -281,47 +373,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">) × 10%. </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">사업자 매입세액 공제</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">(</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">환급</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">) </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">가능</t>
+          <t xml:space="preserve">)</t>
         </r>
       </text>
     </comment>
@@ -333,63 +385,11 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">실제 청구액 입력 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">(</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">특송 통관수수료</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">·</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">관세사 수수료 등</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">)</t>
+          <t xml:space="preserve">실제 송금 수수료 입력</t>
         </r>
       </text>
     </comment>
-    <comment ref="D30" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">실제 송금 수수료 입력</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E23" authorId="0">
+    <comment ref="E22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -493,7 +493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F23" authorId="0">
+    <comment ref="F22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -534,7 +534,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="68">
   <si>
     <r>
       <rPr>
@@ -1606,71 +1606,6 @@
       </rPr>
       <t xml:space="preserve">O</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">재고여부</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미확인 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">결제 후 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일 이내 출고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">미확인</t>
   </si>
   <si>
     <t xml:space="preserve">담당자</t>
@@ -4179,7 +4114,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F49"/>
+  <dimension ref="B2:F48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -4389,200 +4324,196 @@
       <c r="B16" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="15"/>
+      <c r="C16" s="15" t="s">
+        <v>10</v>
+      </c>
       <c r="D16" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>35</v>
+      <c r="F16" s="16" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>8</v>
+      <c r="D21" s="20" t="n">
+        <f aca="false">D7*D9</f>
+        <v>2400</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <f aca="false">E7*E9</f>
+        <v>2800</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <f aca="false">F7*F9</f>
+        <v>2700</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="20" t="n">
-        <f aca="false">D7*D9</f>
-        <v>2400</v>
-      </c>
-      <c r="E22" s="20" t="n">
-        <f aca="false">E7*E9</f>
-        <v>2800</v>
-      </c>
-      <c r="F22" s="20" t="n">
-        <f aca="false">F7*F9</f>
-        <v>2700</v>
-      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="D23" s="20" t="n">
+        <f aca="false">D21+D22</f>
+        <v>2400</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <f aca="false">E21+E22</f>
+        <v>2800</v>
+      </c>
+      <c r="F23" s="20" t="n">
+        <f aca="false">F21+F22</f>
+        <v>2700</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="20" t="n">
-        <f aca="false">D22+D23</f>
-        <v>2400</v>
-      </c>
-      <c r="E24" s="20" t="n">
-        <f aca="false">E22+E23</f>
-        <v>2800</v>
-      </c>
-      <c r="F24" s="20" t="n">
-        <f aca="false">F22+F23</f>
-        <v>2700</v>
+      <c r="D24" s="13" t="n">
+        <f aca="false">D23*$D$2</f>
+        <v>3267600</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <f aca="false">E23*$D$2</f>
+        <v>3812200</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <f aca="false">F23*$D$2</f>
+        <v>3676050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="13" t="n">
-        <f aca="false">D24*$D$2</f>
-        <v>3267600</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <f aca="false">E24*$D$2</f>
-        <v>3812200</v>
-      </c>
-      <c r="F25" s="13" t="n">
-        <f aca="false">F24*$D$2</f>
-        <v>3676050</v>
-      </c>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
+      <c r="D26" s="13" t="n">
+        <f aca="false">ROUND(D24*D25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <f aca="false">ROUND(E24*E25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <f aca="false">ROUND(F24*F25,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="13" t="n">
-        <f aca="false">ROUND(D25*D26,0)</f>
-        <v>0</v>
+        <f aca="false">ROUND((D24+D26)*0.1,0)</f>
+        <v>326760</v>
       </c>
       <c r="E27" s="13" t="n">
-        <f aca="false">ROUND(E25*E26,0)</f>
-        <v>0</v>
+        <f aca="false">ROUND((E24+E26)*0.1,0)</f>
+        <v>381220</v>
       </c>
       <c r="F27" s="13" t="n">
-        <f aca="false">ROUND(F25*F26,0)</f>
-        <v>0</v>
+        <f aca="false">ROUND((F24+F26)*0.1,0)</f>
+        <v>367605</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C28" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="13" t="n">
-        <f aca="false">ROUND((D25+D27)*0.1,0)</f>
-        <v>326760</v>
-      </c>
-      <c r="E28" s="13" t="n">
-        <f aca="false">ROUND((E25+E27)*0.1,0)</f>
-        <v>381220</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <f aca="false">ROUND((F25+F27)*0.1,0)</f>
-        <v>367605</v>
-      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>10</v>
@@ -4592,162 +4523,151 @@
       <c r="F29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="B30" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="19" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*10,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <f aca="false">D24+D26+D27+D28+D29</f>
+        <v>3594360</v>
+      </c>
+      <c r="E30" s="23" t="n">
+        <f aca="false">E24+E26+E27+E28+E29</f>
+        <v>4193420</v>
+      </c>
+      <c r="F30" s="23" t="n">
+        <f aca="false">F24+F26+F27+F28+F29</f>
+        <v>4043655</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="22" t="s">
-        <v>54</v>
+      <c r="B31" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="C31" s="19" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8*10,"-")</f>
+        <f aca="false">IF(ISNUMBER($C$8),$C$8,"-")</f>
         <v>-</v>
       </c>
-      <c r="D31" s="23" t="n">
-        <f aca="false">D25+D27+D28+D29+D30</f>
-        <v>3594360</v>
-      </c>
-      <c r="E31" s="23" t="n">
-        <f aca="false">E25+E27+E28+E29+E30</f>
-        <v>4193420</v>
-      </c>
-      <c r="F31" s="23" t="n">
-        <f aca="false">F25+F27+F28+F29+F30</f>
-        <v>4043655</v>
+      <c r="D31" s="13" t="n">
+        <f aca="false">ROUND(D30/D9,0)</f>
+        <v>359436</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <f aca="false">ROUND(E30/E9,0)</f>
+        <v>419342</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <f aca="false">ROUND(F30/F9,0)</f>
+        <v>404366</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C32" s="19" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8,"-")</f>
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*10,"-")</f>
         <v>-</v>
       </c>
       <c r="D32" s="13" t="n">
-        <f aca="false">ROUND(D31/D9,0)</f>
-        <v>359436</v>
+        <f aca="false">D30-D27</f>
+        <v>3267600</v>
       </c>
       <c r="E32" s="13" t="n">
-        <f aca="false">ROUND(E31/E9,0)</f>
-        <v>419342</v>
+        <f aca="false">E30-E27</f>
+        <v>3812200</v>
       </c>
       <c r="F32" s="13" t="n">
-        <f aca="false">ROUND(F31/F9,0)</f>
-        <v>404366</v>
+        <f aca="false">F30-F27</f>
+        <v>3676050</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="19" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8*10,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <f aca="false">D31-D28</f>
-        <v>3267600</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <f aca="false">E31-E28</f>
-        <v>3812200</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <f aca="false">F31-F28</f>
-        <v>3676050</v>
+        <v>54</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="13" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*D9-D32,"국내단가 입력 필요")</f>
+        <v>국내단가 입력 필요</v>
+      </c>
+      <c r="E33" s="13" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*E9-E32,"국내단가 입력 필요")</f>
+        <v>국내단가 입력 필요</v>
+      </c>
+      <c r="F33" s="13" t="str">
+        <f aca="false">IF(ISNUMBER($C$8),$C$8*F9-F32,"국내단가 입력 필요")</f>
+        <v>국내단가 입력 필요</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="13" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8*D9-D33,"국내단가 입력 필요")</f>
-        <v>국내단가 입력 필요</v>
-      </c>
-      <c r="E34" s="13" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8*E9-E33,"국내단가 입력 필요")</f>
-        <v>국내단가 입력 필요</v>
-      </c>
-      <c r="F34" s="13" t="str">
-        <f aca="false">IF(ISNUMBER($C$8),$C$8*F9-F33,"국내단가 입력 필요")</f>
-        <v>국내단가 입력 필요</v>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="24" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="24" t="s">
-        <v>58</v>
+      <c r="B36" s="25" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="25" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="24" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -4761,9 +4681,9 @@
       <formula>D8=MIN($D$8:$F$8)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D31:F31">
+  <conditionalFormatting sqref="D30:F30">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>D31=MIN($D$31:$F$31)</formula>
+      <formula>D30=MIN($D$30:$F$30)</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
